--- a/scripts/output/beatriz-block-codes.xlsx
+++ b/scripts/output/beatriz-block-codes.xlsx
@@ -1174,7 +1174,7 @@
       <c r="F25" s="10" t="n">
         <v>9895.5</v>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>ALICASA</t>
         </is>
